--- a/resultados/ordenes_detrack.xlsx
+++ b/resultados/ordenes_detrack.xlsx
@@ -433,14 +433,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="39" customWidth="1" min="3" max="3"/>
-    <col width="65" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="49" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
     <col width="26" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
@@ -491,22 +491,22 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>BE008545</t>
+          <t>BE008833</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>IMPRODEMA SAS</t>
+          <t>COMPAÑIA COMUNITARIA METALMECANICA SAS</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>AUT MEDELLIN KM 7 PQ IND CELTA TRADE PARK BG 14</t>
+          <t>CR 32 No 38A - 45 SUR</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -516,12 +516,12 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>69b01c17248b704d49af2b6f</t>
+          <t>6a32a3c5f015781b5caf70b0</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>https://trk.la/anEjhEf</t>
+          <t>https://trk.la/aXgHJPl</t>
         </is>
       </c>
       <c r="H2" s="2" t="n"/>
@@ -529,22 +529,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BE008546</t>
+          <t>BE008834</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>INDUSTRIAS HD S.A.S</t>
+          <t>DIRIMPEX S.A.S</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>KM 2 VIA FUNZA SIBERIA, PARQUE INDUSTRIAL JAPÓN PERÚ BODEGA 6-7</t>
+          <t>CL 18 A No. 68 D - 80</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -554,34 +554,34 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>69b01de90671cc1b25e47a17</t>
+          <t>6a32a5a4a5cec43319dbee8e</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://trk.la/anEEa6f</t>
+          <t>https://trk.la/aXgHoEt</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>BE008556</t>
+          <t>BE008835</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>CONSORCIO METALURGICO NACIONAL S.A.S</t>
+          <t>VIMALUM S.A.S</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>CRA. 14 # 5 A-175 BODEGA 4. Kilometro 19 Mosquera</t>
+          <t>CR 86 C BIS SUR 41 10</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -591,12 +591,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>69b2b80a7cb25e0a9a71f2f2</t>
+          <t>6a32a6dc7597dd3a69347326</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>https://trk.la/anoKC9R</t>
+          <t>https://trk.la/aXgHY2K</t>
         </is>
       </c>
       <c r="H4" s="2" t="n"/>
@@ -604,22 +604,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BE008557</t>
+          <t>BE008836</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>INGENIERIA Y SERVICIOS B &amp; R S.A.S</t>
+          <t>INDUSTRIAL DE RACORES Y PARTES S.A.S INRAPARTES</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CR 92 No 66A - 27</t>
+          <t>CR 27 22 60 BRR SAMPER MENDOZA</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -629,34 +629,34 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69b2ba71f2d0575019043fd2</t>
+          <t>6a32b263dc63756c2fbba8a6</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://trk.la/anoQLm7</t>
+          <t>https://trk.la/aXgIQ0e</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>BE008558</t>
+          <t>BE008837</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>CONSORCIO METALURGICO NACIONAL S.A.S.</t>
+          <t>INDUSTRIAS FABRIMAQ S.A.S</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>TV 60 No. 45 A - 85 SUR</t>
+          <t>CR 64 A No. 5A - 43</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -666,15 +666,127 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>69b309a093cfa461f90702a1</t>
+          <t>6a32b2d6dc63756c2fbba9e6</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>https://trk.la/an2LISX</t>
+          <t>https://trk.la/aXgI7qt</t>
         </is>
       </c>
       <c r="H6" s="2" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>BE008838</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>MECANIZADOS Y TROQUELADOS S.A.S</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>CL 15 No 52 - 14</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>6a32b375dc637503c5f8926e</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://trk.la/aXgIuuO</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>BE008839</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>INGTROMOL SAS</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>CL 37D SUR No 68L -76</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>6a32b3fea5cec46fa5882afe</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>https://trk.la/aXgInEv</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>BE008840</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CARPATEZ GROUP SAS</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>CRT PRINCIPAL PILES VDA PILES</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>dispatched</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>6a32bf96f015783446016484</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://trk.la/aXgVEqn</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
